--- a/slab_detailer/sample_output/sample_slab_bar_schedule.xlsx
+++ b/slab_detailer/sample_output/sample_slab_bar_schedule.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -559,7 +559,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>56ф12x106/20</t>
+          <t>56Φ12x106/20</t>
         </is>
       </c>
     </row>
@@ -611,7 +611,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>31ф12x106/20</t>
+          <t>31Φ12x106/20</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>20ф12x106/20</t>
+          <t>20Φ12x106/20</t>
         </is>
       </c>
     </row>
@@ -715,7 +715,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>57ф12x106/20</t>
+          <t>57Φ12x106/20</t>
         </is>
       </c>
     </row>
@@ -767,7 +767,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>42ф12x106/20</t>
+          <t>42Φ12x106/20</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>20ф12x106/20</t>
+          <t>20Φ12x106/20</t>
         </is>
       </c>
     </row>
@@ -871,7 +871,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>6ф12x120/20</t>
+          <t>6Φ12x120/20</t>
         </is>
       </c>
     </row>
@@ -923,7 +923,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>24ф12x342/20</t>
+          <t>24Φ12x342/20</t>
         </is>
       </c>
     </row>
@@ -975,7 +975,7 @@
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>6ф12x400/20</t>
+          <t>6Φ12x400/20</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>5ф12x472/20</t>
+          <t>5Φ12x472/20</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>24ф12x538/20</t>
+          <t>24Φ12x538/20</t>
         </is>
       </c>
     </row>
@@ -1131,7 +1131,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>5ф12x552/20</t>
+          <t>5Φ12x552/20</t>
         </is>
       </c>
     </row>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>24ф12x596/20</t>
+          <t>24Φ12x596/20</t>
         </is>
       </c>
     </row>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>13ф12x596/20</t>
+          <t>13Φ12x596/20</t>
         </is>
       </c>
     </row>
@@ -1287,7 +1287,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>13ф12x596/20</t>
+          <t>13Φ12x596/20</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>137ф12x600/20</t>
+          <t>137Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>57ф12x600/20</t>
+          <t>57Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1443,7 +1443,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>57ф12x600/20</t>
+          <t>57Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1495,7 +1495,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>57ф12x600/20</t>
+          <t>57Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1547,7 +1547,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>56ф12x600/20</t>
+          <t>56Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>56ф12x600/20</t>
+          <t>56Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1651,7 +1651,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>56ф12x600/20</t>
+          <t>56Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>56ф12x600/20</t>
+          <t>56Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>31ф12x600/20</t>
+          <t>31Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>24ф12x600/20</t>
+          <t>24Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1859,7 +1859,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>20ф12x600/20</t>
+          <t>20Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1896,7 +1896,7 @@
         <v>6000</v>
       </c>
       <c r="H28" t="n">
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="I28" s="2">
         <f>G28*H28/1000</f>
@@ -1911,7 +1911,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>112ф12x600/20</t>
+          <t>137Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>57ф12x600/20</t>
+          <t>57Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>57ф12x600/20</t>
+          <t>57Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>57ф12x600/20</t>
+          <t>57Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2119,7 +2119,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>57ф12x600/20</t>
+          <t>57Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2171,7 +2171,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>42ф12x600/20</t>
+          <t>42Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>42ф12x600/20</t>
+          <t>42Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>42ф12x600/20</t>
+          <t>42Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2327,7 +2327,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>42ф12x600/20</t>
+          <t>42Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2379,7 +2379,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>20ф12x600/20</t>
+          <t>20Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>20ф12x600/20</t>
+          <t>20Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>20ф12x600/20</t>
+          <t>20Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2535,7 +2535,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>20ф12x600/20</t>
+          <t>20Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2572,7 +2572,7 @@
         <v>6000</v>
       </c>
       <c r="H41" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I41" s="2">
         <f>G41*H41/1000</f>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>20ф12x600/20</t>
+          <t>13Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
         <v>6000</v>
       </c>
       <c r="H42" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I42" s="2">
         <f>G42*H42/1000</f>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>13ф12x600/20</t>
+          <t>5Φ12x600/20</t>
         </is>
       </c>
     </row>
@@ -2691,14 +2691,14 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>5ф12x600/20</t>
+          <t>5Φ12x600/20</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>N9</t>
+          <t>N10</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2717,7 +2717,7 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2725,7 +2725,7 @@
         </is>
       </c>
       <c r="G44" t="n">
-        <v>6000</v>
+        <v>2020</v>
       </c>
       <c r="H44" t="n">
         <v>5</v>
@@ -2735,7 +2735,7 @@
         <v/>
       </c>
       <c r="J44" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K44" s="3">
         <f>I44*J44</f>
@@ -2743,14 +2743,14 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>5ф12x600/20</t>
+          <t>5Φ14x202/20</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>N9</t>
+          <t>N11</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -2760,7 +2760,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bottom</t>
+          <t>Top</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2777,17 +2777,17 @@
         </is>
       </c>
       <c r="G45" t="n">
-        <v>6000</v>
+        <v>2880</v>
       </c>
       <c r="H45" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I45" s="2">
         <f>G45*H45/1000</f>
         <v/>
       </c>
       <c r="J45" t="n">
-        <v>0.888</v>
+        <v>1.208</v>
       </c>
       <c r="K45" s="3">
         <f>I45*J45</f>
@@ -2795,14 +2795,14 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>5ф12x600/20</t>
+          <t>13Φ14x288/20</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>N10</t>
+          <t>N12</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2817,7 +2817,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2829,10 +2829,10 @@
         </is>
       </c>
       <c r="G46" t="n">
-        <v>2020</v>
+        <v>2980</v>
       </c>
       <c r="H46" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I46" s="2">
         <f>G46*H46/1000</f>
@@ -2847,14 +2847,14 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>5ф14x202/20</t>
+          <t>24Φ14x298/20</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>N11</t>
+          <t>N12</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2881,7 +2881,7 @@
         </is>
       </c>
       <c r="G47" t="n">
-        <v>2880</v>
+        <v>2980</v>
       </c>
       <c r="H47" t="n">
         <v>13</v>
@@ -2899,14 +2899,14 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>13ф14x288/20</t>
+          <t>13Φ14x298/20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>N12</t>
+          <t>N13</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2933,7 +2933,7 @@
         </is>
       </c>
       <c r="G48" t="n">
-        <v>2980</v>
+        <v>3000</v>
       </c>
       <c r="H48" t="n">
         <v>24</v>
@@ -2951,14 +2951,14 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>24ф14x298/20</t>
+          <t>24Φ14x300/20</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>N12</t>
+          <t>N14</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2985,10 +2985,10 @@
         </is>
       </c>
       <c r="G49" t="n">
-        <v>2980</v>
+        <v>3380</v>
       </c>
       <c r="H49" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I49" s="2">
         <f>G49*H49/1000</f>
@@ -3003,14 +3003,14 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>13ф14x298/20</t>
+          <t>5Φ14x338/20</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>N13</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3037,10 +3037,10 @@
         </is>
       </c>
       <c r="G50" t="n">
-        <v>3000</v>
+        <v>3620</v>
       </c>
       <c r="H50" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="I50" s="2">
         <f>G50*H50/1000</f>
@@ -3055,14 +3055,14 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>24ф14x300/20</t>
+          <t>56Φ14x362/20</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>N14</t>
+          <t>N15</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -3089,10 +3089,10 @@
         </is>
       </c>
       <c r="G51" t="n">
-        <v>3380</v>
+        <v>3620</v>
       </c>
       <c r="H51" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="I51" s="2">
         <f>G51*H51/1000</f>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>5ф14x338/20</t>
+          <t>31Φ14x362/20</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3144,7 @@
         <v>3620</v>
       </c>
       <c r="H52" t="n">
-        <v>56</v>
+        <v>20</v>
       </c>
       <c r="I52" s="2">
         <f>G52*H52/1000</f>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>56ф14x362/20</t>
+          <t>20Φ14x362/20</t>
         </is>
       </c>
     </row>
@@ -3181,7 +3181,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -3196,7 +3196,7 @@
         <v>3620</v>
       </c>
       <c r="H53" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I53" s="2">
         <f>G53*H53/1000</f>
@@ -3211,7 +3211,7 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>31ф14x362/20</t>
+          <t>57Φ14x362/20</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3233,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -3248,7 +3248,7 @@
         <v>3620</v>
       </c>
       <c r="H54" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="I54" s="2">
         <f>G54*H54/1000</f>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>20ф14x362/20</t>
+          <t>42Φ14x362/20</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v>3620</v>
       </c>
       <c r="H55" t="n">
-        <v>57</v>
+        <v>20</v>
       </c>
       <c r="I55" s="2">
         <f>G55*H55/1000</f>
@@ -3315,14 +3315,14 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>57ф14x362/20</t>
+          <t>20Φ14x362/20</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3337,7 +3337,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E56" t="n">
@@ -3349,10 +3349,10 @@
         </is>
       </c>
       <c r="G56" t="n">
-        <v>3620</v>
+        <v>3680</v>
       </c>
       <c r="H56" t="n">
-        <v>42</v>
+        <v>6</v>
       </c>
       <c r="I56" s="2">
         <f>G56*H56/1000</f>
@@ -3367,14 +3367,14 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>42ф14x362/20</t>
+          <t>6Φ14x368/20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>N15</t>
+          <t>N17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -3401,10 +3401,10 @@
         </is>
       </c>
       <c r="G57" t="n">
-        <v>3620</v>
+        <v>3920</v>
       </c>
       <c r="H57" t="n">
-        <v>20</v>
+        <v>137</v>
       </c>
       <c r="I57" s="2">
         <f>G57*H57/1000</f>
@@ -3419,14 +3419,14 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>20ф14x362/20</t>
+          <t>137Φ14x392/20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>N16</t>
+          <t>N17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -3453,10 +3453,10 @@
         </is>
       </c>
       <c r="G58" t="n">
-        <v>3680</v>
+        <v>3920</v>
       </c>
       <c r="H58" t="n">
-        <v>6</v>
+        <v>112</v>
       </c>
       <c r="I58" s="2">
         <f>G58*H58/1000</f>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>6ф14x368/20</t>
+          <t>112Φ14x392/20</t>
         </is>
       </c>
     </row>
@@ -3493,7 +3493,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -3508,7 +3508,7 @@
         <v>3920</v>
       </c>
       <c r="H59" t="n">
-        <v>137</v>
+        <v>20</v>
       </c>
       <c r="I59" s="2">
         <f>G59*H59/1000</f>
@@ -3523,14 +3523,14 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>137ф14x392/20</t>
+          <t>20Φ14x392/20</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>N17</t>
+          <t>N18</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -3545,7 +3545,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -3557,10 +3557,10 @@
         </is>
       </c>
       <c r="G60" t="n">
-        <v>3920</v>
+        <v>4000</v>
       </c>
       <c r="H60" t="n">
-        <v>112</v>
+        <v>6</v>
       </c>
       <c r="I60" s="2">
         <f>G60*H60/1000</f>
@@ -3575,14 +3575,14 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>112ф14x392/20</t>
+          <t>6Φ14x400/20</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>N17</t>
+          <t>N19</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -3609,10 +3609,10 @@
         </is>
       </c>
       <c r="G61" t="n">
-        <v>3920</v>
+        <v>4020</v>
       </c>
       <c r="H61" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="I61" s="2">
         <f>G61*H61/1000</f>
@@ -3627,14 +3627,14 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>20ф14x392/20</t>
+          <t>13Φ14x402/20</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>N18</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -3661,10 +3661,10 @@
         </is>
       </c>
       <c r="G62" t="n">
-        <v>4000</v>
+        <v>6000</v>
       </c>
       <c r="H62" t="n">
-        <v>6</v>
+        <v>137</v>
       </c>
       <c r="I62" s="2">
         <f>G62*H62/1000</f>
@@ -3679,14 +3679,14 @@
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>6ф14x400/20</t>
+          <t>137Φ14x600/20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>N19</t>
+          <t>N20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Y</t>
+          <t>X</t>
         </is>
       </c>
       <c r="E63" t="n">
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="G63" t="n">
-        <v>4020</v>
+        <v>6000</v>
       </c>
       <c r="H63" t="n">
-        <v>13</v>
+        <v>57</v>
       </c>
       <c r="I63" s="2">
         <f>G63*H63/1000</f>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>13ф14x402/20</t>
+          <t>57Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
         <v>6000</v>
       </c>
       <c r="H64" t="n">
-        <v>137</v>
+        <v>57</v>
       </c>
       <c r="I64" s="2">
         <f>G64*H64/1000</f>
@@ -3783,7 +3783,7 @@
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>137ф14x600/20</t>
+          <t>57Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -3820,7 +3820,7 @@
         <v>6000</v>
       </c>
       <c r="H65" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I65" s="2">
         <f>G65*H65/1000</f>
@@ -3835,7 +3835,7 @@
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>57ф14x600/20</t>
+          <t>56Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -3872,7 +3872,7 @@
         <v>6000</v>
       </c>
       <c r="H66" t="n">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I66" s="2">
         <f>G66*H66/1000</f>
@@ -3887,7 +3887,7 @@
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>57ф14x600/20</t>
+          <t>56Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>56ф14x600/20</t>
+          <t>56Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
         <v>6000</v>
       </c>
       <c r="H68" t="n">
-        <v>56</v>
+        <v>31</v>
       </c>
       <c r="I68" s="2">
         <f>G68*H68/1000</f>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>56ф14x600/20</t>
+          <t>31Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4028,7 +4028,7 @@
         <v>6000</v>
       </c>
       <c r="H69" t="n">
-        <v>56</v>
+        <v>24</v>
       </c>
       <c r="I69" s="2">
         <f>G69*H69/1000</f>
@@ -4043,7 +4043,7 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>56ф14x600/20</t>
+          <t>24Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4080,7 +4080,7 @@
         <v>6000</v>
       </c>
       <c r="H70" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="I70" s="2">
         <f>G70*H70/1000</f>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>31ф14x600/20</t>
+          <t>24Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4132,7 @@
         <v>6000</v>
       </c>
       <c r="H71" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="I71" s="2">
         <f>G71*H71/1000</f>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>24ф14x600/20</t>
+          <t>20Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -4184,7 +4184,7 @@
         <v>6000</v>
       </c>
       <c r="H72" t="n">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="I72" s="2">
         <f>G72*H72/1000</f>
@@ -4199,7 +4199,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>24ф14x600/20</t>
+          <t>112Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4221,7 +4221,7 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>Y</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -4236,7 +4236,7 @@
         <v>6000</v>
       </c>
       <c r="H73" t="n">
-        <v>20</v>
+        <v>67</v>
       </c>
       <c r="I73" s="2">
         <f>G73*H73/1000</f>
@@ -4251,7 +4251,7 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>20ф14x600/20</t>
+          <t>67Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4288,7 +4288,7 @@
         <v>6000</v>
       </c>
       <c r="H74" t="n">
-        <v>112</v>
+        <v>67</v>
       </c>
       <c r="I74" s="2">
         <f>G74*H74/1000</f>
@@ -4303,7 +4303,7 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>112ф14x600/20</t>
+          <t>67Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4340,7 +4340,7 @@
         <v>6000</v>
       </c>
       <c r="H75" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="I75" s="2">
         <f>G75*H75/1000</f>
@@ -4355,7 +4355,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>57ф14x600/20</t>
+          <t>67Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>57ф14x600/20</t>
+          <t>57Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4459,7 +4459,7 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>57ф14x600/20</t>
+          <t>57Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4496,7 +4496,7 @@
         <v>6000</v>
       </c>
       <c r="H78" t="n">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="I78" s="2">
         <f>G78*H78/1000</f>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>42ф14x600/20</t>
+          <t>57Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4548,7 @@
         <v>6000</v>
       </c>
       <c r="H79" t="n">
-        <v>42</v>
+        <v>20</v>
       </c>
       <c r="I79" s="2">
         <f>G79*H79/1000</f>
@@ -4563,7 +4563,7 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>42ф14x600/20</t>
+          <t>20Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
         <v>6000</v>
       </c>
       <c r="H80" t="n">
-        <v>42</v>
+        <v>13</v>
       </c>
       <c r="I80" s="2">
         <f>G80*H80/1000</f>
@@ -4615,7 +4615,7 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>42ф14x600/20</t>
+          <t>13Φ14x600/20</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
         <v>6000</v>
       </c>
       <c r="H81" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="I81" s="2">
         <f>G81*H81/1000</f>
@@ -4667,452 +4667,36 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>20ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>14</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H82" t="n">
-        <v>20</v>
-      </c>
-      <c r="I82" s="2">
-        <f>G82*H82/1000</f>
-        <v/>
-      </c>
-      <c r="J82" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K82" s="3">
-        <f>I82*J82</f>
-        <v/>
-      </c>
-      <c r="L82" t="inlineStr">
-        <is>
-          <t>20ф14x600/20</t>
+          <t>5Φ14x600/20</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
-        <v>14</v>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H83" t="n">
-        <v>20</v>
-      </c>
-      <c r="I83" s="2">
-        <f>G83*H83/1000</f>
-        <v/>
-      </c>
-      <c r="J83" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K83" s="3">
-        <f>I83*J83</f>
-        <v/>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>20ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E84" t="n">
-        <v>14</v>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G84" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H84" t="n">
-        <v>20</v>
-      </c>
-      <c r="I84" s="2">
-        <f>G84*H84/1000</f>
-        <v/>
-      </c>
-      <c r="J84" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K84" s="3">
-        <f>I84*J84</f>
-        <v/>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>20ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E85" t="n">
-        <v>14</v>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G85" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H85" t="n">
-        <v>13</v>
-      </c>
-      <c r="I85" s="2">
-        <f>G85*H85/1000</f>
-        <v/>
-      </c>
-      <c r="J85" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K85" s="3">
-        <f>I85*J85</f>
-        <v/>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>13ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E86" t="n">
-        <v>14</v>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G86" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H86" t="n">
-        <v>5</v>
-      </c>
-      <c r="I86" s="2">
-        <f>G86*H86/1000</f>
-        <v/>
-      </c>
-      <c r="J86" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K86" s="3">
-        <f>I86*J86</f>
-        <v/>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>5ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E87" t="n">
-        <v>14</v>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G87" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H87" t="n">
-        <v>5</v>
-      </c>
-      <c r="I87" s="2">
-        <f>G87*H87/1000</f>
-        <v/>
-      </c>
-      <c r="J87" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K87" s="3">
-        <f>I87*J87</f>
-        <v/>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>5ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E88" t="n">
-        <v>14</v>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H88" t="n">
-        <v>5</v>
-      </c>
-      <c r="I88" s="2">
-        <f>G88*H88/1000</f>
-        <v/>
-      </c>
-      <c r="J88" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K88" s="3">
-        <f>I88*J88</f>
-        <v/>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>5ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>N20</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Mesh</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Top</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="E89" t="n">
-        <v>14</v>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>straight</t>
-        </is>
-      </c>
-      <c r="G89" t="n">
-        <v>6000</v>
-      </c>
-      <c r="H89" t="n">
-        <v>5</v>
-      </c>
-      <c r="I89" s="2">
-        <f>G89*H89/1000</f>
-        <v/>
-      </c>
-      <c r="J89" t="n">
-        <v>1.208</v>
-      </c>
-      <c r="K89" s="3">
-        <f>I89*J89</f>
-        <v/>
-      </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t>5ф14x600/20</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="4" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B91" s="4" t="inlineStr"/>
-      <c r="C91" s="4" t="inlineStr"/>
-      <c r="D91" s="4" t="inlineStr"/>
-      <c r="E91" s="4" t="inlineStr"/>
-      <c r="F91" s="4" t="inlineStr"/>
-      <c r="G91" s="4" t="inlineStr"/>
-      <c r="H91" s="4">
-        <f>SUM(H2:H89)</f>
-        <v/>
-      </c>
-      <c r="I91" s="4">
-        <f>SUM(I2:I89)</f>
-        <v/>
-      </c>
-      <c r="J91" s="4" t="inlineStr"/>
-      <c r="K91" s="4">
-        <f>SUM(K2:K89)</f>
-        <v/>
-      </c>
-      <c r="L91" s="4" t="n"/>
+      <c r="B83" s="4" t="inlineStr"/>
+      <c r="C83" s="4" t="inlineStr"/>
+      <c r="D83" s="4" t="inlineStr"/>
+      <c r="E83" s="4" t="inlineStr"/>
+      <c r="F83" s="4" t="inlineStr"/>
+      <c r="G83" s="4" t="inlineStr"/>
+      <c r="H83" s="4">
+        <f>SUM(H2:H81)</f>
+        <v/>
+      </c>
+      <c r="I83" s="4">
+        <f>SUM(I2:I81)</f>
+        <v/>
+      </c>
+      <c r="J83" s="4" t="inlineStr"/>
+      <c r="K83" s="4">
+        <f>SUM(K2:K81)</f>
+        <v/>
+      </c>
+      <c r="L83" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5161,7 +4745,7 @@
         <v>12</v>
       </c>
       <c r="B2" s="3">
-        <f>SUMIF('Bar schedule'!E2:E89,A2,'Bar schedule'!I2:I89)</f>
+        <f>SUMIF('Bar schedule'!E2:E81,A2,'Bar schedule'!I2:I81)</f>
         <v/>
       </c>
       <c r="C2" t="n">
@@ -5177,7 +4761,7 @@
         <v>14</v>
       </c>
       <c r="B3" s="3">
-        <f>SUMIF('Bar schedule'!E2:E89,A3,'Bar schedule'!I2:I89)</f>
+        <f>SUMIF('Bar schedule'!E2:E81,A3,'Bar schedule'!I2:I81)</f>
         <v/>
       </c>
       <c r="C3" t="n">
